--- a/files/excel-mastery-2-1-sumifs.xlsx
+++ b/files/excel-mastery-2-1-sumifs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2-1_実績集計_SUMIFS" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1602,329 +1605,329 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="D7" s="171" t="inlineStr">
+      <c r="D7" s="168" t="inlineStr">
         <is>
           <t>予約ID</t>
         </is>
       </c>
-      <c r="E7" s="171" t="inlineStr">
+      <c r="E7" s="168" t="inlineStr">
         <is>
           <t>施設</t>
         </is>
       </c>
-      <c r="F7" s="171" t="inlineStr">
+      <c r="F7" s="168" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="G7" s="171" t="inlineStr">
+      <c r="G7" s="168" t="inlineStr">
         <is>
           <t>客室タイプ</t>
         </is>
       </c>
-      <c r="H7" s="171" t="inlineStr">
+      <c r="H7" s="168" t="inlineStr">
         <is>
           <t>泊数</t>
         </is>
       </c>
-      <c r="I7" s="171" t="inlineStr">
+      <c r="I7" s="168" t="inlineStr">
         <is>
           <t>宿泊人数</t>
         </is>
       </c>
-      <c r="J7" s="171" t="inlineStr">
+      <c r="J7" s="168" t="inlineStr">
         <is>
           <t>売上(円)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="D8" s="172" t="inlineStr">
+      <c r="D8" s="169" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="E8" s="172" t="inlineStr">
+      <c r="E8" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F8" s="189" t="n">
+      <c r="F8" s="186" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="172" t="inlineStr">
+      <c r="G8" s="169" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H8" s="173" t="n">
+      <c r="H8" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="173" t="n">
+      <c r="I8" s="170" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="173" t="n">
+      <c r="J8" s="170" t="n">
         <v>160000</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="D9" s="172" t="inlineStr">
+      <c r="D9" s="169" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="E9" s="172" t="inlineStr">
+      <c r="E9" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F9" s="189" t="n">
+      <c r="F9" s="186" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="172" t="inlineStr">
+      <c r="G9" s="169" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H9" s="173" t="n">
+      <c r="H9" s="170" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="173" t="n">
+      <c r="I9" s="170" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="173" t="n">
+      <c r="J9" s="170" t="n">
         <v>108000</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="D10" s="172" t="inlineStr">
+      <c r="D10" s="169" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="E10" s="172" t="inlineStr">
+      <c r="E10" s="169" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F10" s="189" t="n">
+      <c r="F10" s="186" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="172" t="inlineStr">
+      <c r="G10" s="169" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H10" s="173" t="n">
+      <c r="H10" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="173" t="n">
+      <c r="I10" s="170" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="173" t="n">
+      <c r="J10" s="170" t="n">
         <v>72000</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="D11" s="172" t="inlineStr">
+      <c r="D11" s="169" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="E11" s="172" t="inlineStr">
+      <c r="E11" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F11" s="189" t="n">
+      <c r="F11" s="186" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="172" t="inlineStr">
+      <c r="G11" s="169" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H11" s="173" t="n">
+      <c r="H11" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="173" t="n">
+      <c r="I11" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="173" t="n">
+      <c r="J11" s="170" t="n">
         <v>180000</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="D12" s="172" t="inlineStr">
+      <c r="D12" s="169" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="E12" s="172" t="inlineStr">
+      <c r="E12" s="169" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F12" s="189" t="n">
+      <c r="F12" s="186" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="172" t="inlineStr">
+      <c r="G12" s="169" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H12" s="173" t="n">
+      <c r="H12" s="170" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="173" t="n">
+      <c r="I12" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="173" t="n">
+      <c r="J12" s="170" t="n">
         <v>95000</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="D13" s="172" t="inlineStr">
+      <c r="D13" s="169" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="E13" s="172" t="inlineStr">
+      <c r="E13" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F13" s="189" t="n">
+      <c r="F13" s="186" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="172" t="inlineStr">
+      <c r="G13" s="169" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H13" s="173" t="n">
+      <c r="H13" s="170" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="173" t="n">
+      <c r="I13" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="173" t="n">
+      <c r="J13" s="170" t="n">
         <v>36000</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="D14" s="172" t="inlineStr">
+      <c r="D14" s="169" t="inlineStr">
         <is>
           <t>R007</t>
         </is>
       </c>
-      <c r="E14" s="172" t="inlineStr">
+      <c r="E14" s="169" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F14" s="189" t="n">
+      <c r="F14" s="186" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="172" t="inlineStr">
+      <c r="G14" s="169" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H14" s="173" t="n">
+      <c r="H14" s="170" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="173" t="n">
+      <c r="I14" s="170" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="173" t="n">
+      <c r="J14" s="170" t="n">
         <v>152000</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="D15" s="172" t="inlineStr">
+      <c r="D15" s="169" t="inlineStr">
         <is>
           <t>R008</t>
         </is>
       </c>
-      <c r="E15" s="172" t="inlineStr">
+      <c r="E15" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F15" s="189" t="n">
+      <c r="F15" s="186" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="172" t="inlineStr">
+      <c r="G15" s="169" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H15" s="173" t="n">
+      <c r="H15" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="173" t="n">
+      <c r="I15" s="170" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="173" t="n">
+      <c r="J15" s="170" t="n">
         <v>74000</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="D16" s="172" t="inlineStr">
+      <c r="D16" s="169" t="inlineStr">
         <is>
           <t>R009</t>
         </is>
       </c>
-      <c r="E16" s="172" t="inlineStr">
+      <c r="E16" s="169" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F16" s="189" t="n">
+      <c r="F16" s="186" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="172" t="inlineStr">
+      <c r="G16" s="169" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H16" s="173" t="n">
+      <c r="H16" s="170" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="173" t="n">
+      <c r="I16" s="170" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="173" t="n">
+      <c r="J16" s="170" t="n">
         <v>92000</v>
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="D17" s="172" t="inlineStr">
+      <c r="D17" s="169" t="inlineStr">
         <is>
           <t>R010</t>
         </is>
       </c>
-      <c r="E17" s="172" t="inlineStr">
+      <c r="E17" s="169" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F17" s="189" t="n">
+      <c r="F17" s="186" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="172" t="inlineStr">
+      <c r="G17" s="169" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H17" s="173" t="n">
+      <c r="H17" s="170" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="173" t="n">
+      <c r="I17" s="170" t="n">
         <v>5</v>
       </c>
-      <c r="J17" s="173" t="n">
+      <c r="J17" s="170" t="n">
         <v>270000</v>
       </c>
     </row>
